--- a/LushProtein_Source_to_Target_Mapping_ExerciseV1.xlsx
+++ b/LushProtein_Source_to_Target_Mapping_ExerciseV1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adity\Documents\Aditya SMU\SMU Sem 5\Lush Protein SMU X\LushProtein_Project_Data_20260505\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DF33AF8-9E2A-47D9-90EE-60F4EB492088}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{434B9EA1-E01F-4364-90F9-69F5E5DDF372}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{52D93540-DB92-4EA1-BA97-BBD53217CD64}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="172">
   <si>
     <t>Instructions to ISSS603 Class: Create a STTM for Orders dataset</t>
   </si>
@@ -90,6 +90,471 @@
   </si>
   <si>
     <t>Shopify order PK.</t>
+  </si>
+  <si>
+    <t>order_name</t>
+  </si>
+  <si>
+    <t>STRING</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>text</t>
+  </si>
+  <si>
+    <t>Human-readable order number. Prefix encodes store: LP/LPSG=SG, LPMY=MY, LPHK=HK.</t>
+  </si>
+  <si>
+    <t>order_date</t>
+  </si>
+  <si>
+    <t>DATETIME</t>
+  </si>
+  <si>
+    <t>Processed At</t>
+  </si>
+  <si>
+    <t>datetime+tz</t>
+  </si>
+  <si>
+    <t>Parse UTC; convert to Asia/Singapore; normalize to date.</t>
+  </si>
+  <si>
+    <t>Use Processed At (payment time) not Created At.</t>
+  </si>
+  <si>
+    <t>customer_id</t>
+  </si>
+  <si>
+    <t>FK -&gt; customers</t>
+  </si>
+  <si>
+    <t>Customer: ID</t>
+  </si>
+  <si>
+    <t>Filter Top Row = 1; cast STRING; drop nulls.</t>
+  </si>
+  <si>
+    <t>Links to customer entity.</t>
+  </si>
+  <si>
+    <t>store</t>
+  </si>
+  <si>
+    <t>STRING (cat)</t>
+  </si>
+  <si>
+    <t>Name (derived)</t>
+  </si>
+  <si>
+    <t>CASE WHEN Name starts LPMY-&gt;MY, LPHK-&gt;HK, LPSG/LP-&gt;SG ELSE Other.</t>
+  </si>
+  <si>
+    <t>Derived column â€” not in raw export. Implemented in 01_load_and_merge.py.</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Direct copy at load; post-FX all rows set to SGD in pipeline.</t>
+  </si>
+  <si>
+    <t>Raw: SGD/MYR/HKD mixed. Never sum across currencies before FX.</t>
+  </si>
+  <si>
+    <t>total_price</t>
+  </si>
+  <si>
+    <t>DECIMAL</t>
+  </si>
+  <si>
+    <t>Price: Total</t>
+  </si>
+  <si>
+    <t>decimal</t>
+  </si>
+  <si>
+    <t>Numeric cast; multiply by FX_RATES_TO_SGD[store] at load.</t>
+  </si>
+  <si>
+    <t>Net order revenue in SGD after FX conversion.</t>
+  </si>
+  <si>
+    <t>total_discount</t>
+  </si>
+  <si>
+    <t>Price: Total Discount</t>
+  </si>
+  <si>
+    <t>Numeric cast; fill null-&gt;0; multiply by FX rate.</t>
+  </si>
+  <si>
+    <t>Order-level discount amount in SGD.</t>
+  </si>
+  <si>
+    <t>total_shipping</t>
+  </si>
+  <si>
+    <t>Price: Total Shipping</t>
+  </si>
+  <si>
+    <t>Shipping charged on order.</t>
+  </si>
+  <si>
+    <t>payment_status</t>
+  </si>
+  <si>
+    <t>Payment: Status</t>
+  </si>
+  <si>
+    <t>Direct copy; keep paid and partially_refunded only.</t>
+  </si>
+  <si>
+    <t>Exclude unpaid/cancelled before payment.</t>
+  </si>
+  <si>
+    <t>fulfillment_status</t>
+  </si>
+  <si>
+    <t>Order Fulfillment Status</t>
+  </si>
+  <si>
+    <t>Direct copy; exclude restocked.</t>
+  </si>
+  <si>
+    <t>restocked rows removed in 01_load_and_merge.py.</t>
+  </si>
+  <si>
+    <t>tags</t>
+  </si>
+  <si>
+    <t>Tags</t>
+  </si>
+  <si>
+    <t>text (comma-list)</t>
+  </si>
+  <si>
+    <t>Direct copy; parse for subscription/marketplace signals.</t>
+  </si>
+  <si>
+    <t>62% null. Key: Subscription Order, FIRST_ORDER, shopee, lazada.</t>
+  </si>
+  <si>
+    <t>order_source</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>Filter Top Row=1; lower-case; direct copy.</t>
+  </si>
+  <si>
+    <t>Shopify order source: web, pos, subscription_contract, shopee, etc. pos = on-site (Shopify POS).</t>
+  </si>
+  <si>
+    <t>utm_source</t>
+  </si>
+  <si>
+    <t>Browser: UTM Source</t>
+  </si>
+  <si>
+    <t>Direct copy.</t>
+  </si>
+  <si>
+    <t>94.9% null. Used in classify_channel when present.</t>
+  </si>
+  <si>
+    <t>utm_medium</t>
+  </si>
+  <si>
+    <t>Browser: UTM Medium</t>
+  </si>
+  <si>
+    <t>Companion to utm_source.</t>
+  </si>
+  <si>
+    <t>utm_campaign</t>
+  </si>
+  <si>
+    <t>Browser: UTM Campaign</t>
+  </si>
+  <si>
+    <t>Campaign name string.</t>
+  </si>
+  <si>
+    <t>shipping_country</t>
+  </si>
+  <si>
+    <t>Shipping: Country</t>
+  </si>
+  <si>
+    <t>Top: Malaysia 52%, Singapore 41%.</t>
+  </si>
+  <si>
+    <t>cancelled_at</t>
+  </si>
+  <si>
+    <t>Cancelled At</t>
+  </si>
+  <si>
+    <t>datetime</t>
+  </si>
+  <si>
+    <t>Parse datetime; null = not cancelled.</t>
+  </si>
+  <si>
+    <t>89% null.</t>
+  </si>
+  <si>
+    <t>channel</t>
+  </si>
+  <si>
+    <t>Tags + Browser: UTM Source + Name (derived)</t>
+  </si>
+  <si>
+    <t>classify_channel() in 00_config.py.</t>
+  </si>
+  <si>
+    <t>Derived: Subscription | Marketplace | Direct/Organic | Paid Social | Email | Affiliate | Paid Search.</t>
+  </si>
+  <si>
+    <t>product_category</t>
+  </si>
+  <si>
+    <t>Line: Product Handle (derived)</t>
+  </si>
+  <si>
+    <t>classify_product() keyword map in 00_config.py.</t>
+  </si>
+  <si>
+    <t>Derived from first line handle on Top Row. Not a product-master join.</t>
+  </si>
+  <si>
+    <t>has_discount</t>
+  </si>
+  <si>
+    <t>BOOL</t>
+  </si>
+  <si>
+    <t>Price: Total Discount (derived)</t>
+  </si>
+  <si>
+    <t>bool</t>
+  </si>
+  <si>
+    <t>total_discount &gt; 0.</t>
+  </si>
+  <si>
+    <t>Flag for discounted orders.</t>
+  </si>
+  <si>
+    <t>is_subscription</t>
+  </si>
+  <si>
+    <t>Tags (derived)</t>
+  </si>
+  <si>
+    <t>Tags contains subscription|yotpo subscriptions (case-insensitive).</t>
+  </si>
+  <si>
+    <t>Shopify-trackable subscriptions only.</t>
+  </si>
+  <si>
+    <t>is_first_order_tag</t>
+  </si>
+  <si>
+    <t>Tags contains FIRST_ORDER.</t>
+  </si>
+  <si>
+    <t>Tag-based first order indicator.</t>
+  </si>
+  <si>
+    <t>line_id</t>
+  </si>
+  <si>
+    <t>PK (line-level)</t>
+  </si>
+  <si>
+    <t>Line: ID</t>
+  </si>
+  <si>
+    <t>id</t>
+  </si>
+  <si>
+    <t>Filter Line: Type = Line Item; cast STRING.</t>
+  </si>
+  <si>
+    <t>Line-level PK for product analysis.</t>
+  </si>
+  <si>
+    <t>line_product_handle</t>
+  </si>
+  <si>
+    <t>FK -&gt; products</t>
+  </si>
+  <si>
+    <t>Line: Product Handle</t>
+  </si>
+  <si>
+    <t>text (slug)</t>
+  </si>
+  <si>
+    <t>Filter Line: Type = Line Item; direct copy.</t>
+  </si>
+  <si>
+    <t>Join key to products_master.Handle.</t>
+  </si>
+  <si>
+    <t>line_sku</t>
+  </si>
+  <si>
+    <t>Line: SKU</t>
+  </si>
+  <si>
+    <t>Filter Line: Type = Line Item; cast STRING preserve leading zeros.</t>
+  </si>
+  <si>
+    <t>Join key to products_master.Variant SKU.</t>
+  </si>
+  <si>
+    <t>line_title</t>
+  </si>
+  <si>
+    <t>Line: Title</t>
+  </si>
+  <si>
+    <t>Product display name.</t>
+  </si>
+  <si>
+    <t>line_variant_title</t>
+  </si>
+  <si>
+    <t>Line: Variant Title</t>
+  </si>
+  <si>
+    <t>Flavor/pack size label â€” use for flavor-level analysis.</t>
+  </si>
+  <si>
+    <t>line_quantity</t>
+  </si>
+  <si>
+    <t>INT</t>
+  </si>
+  <si>
+    <t>Line: Quantity</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>Cast INT.</t>
+  </si>
+  <si>
+    <t>Units purchased.</t>
+  </si>
+  <si>
+    <t>line_price</t>
+  </si>
+  <si>
+    <t>Line: Price</t>
+  </si>
+  <si>
+    <t>Numeric cast; multiply by FX rate.</t>
+  </si>
+  <si>
+    <t>Unit price before line discount (SGD).</t>
+  </si>
+  <si>
+    <t>line_discount</t>
+  </si>
+  <si>
+    <t>Line: Discount</t>
+  </si>
+  <si>
+    <t>Line-level discount (SGD).</t>
+  </si>
+  <si>
+    <t>line_total</t>
+  </si>
+  <si>
+    <t>Line: Total</t>
+  </si>
+  <si>
+    <t>Line revenue after discount (SGD).</t>
+  </si>
+  <si>
+    <t>total_revenue</t>
+  </si>
+  <si>
+    <t>orders.parquet (derived)</t>
+  </si>
+  <si>
+    <t>SUM(Price: Total) GROUP BY customer_id.</t>
+  </si>
+  <si>
+    <t>Customer LTV definition used in finals analysis.</t>
+  </si>
+  <si>
+    <t>is_repeat</t>
+  </si>
+  <si>
+    <t>customers.parquet (derived)</t>
+  </si>
+  <si>
+    <t>order count (derived)</t>
+  </si>
+  <si>
+    <t>total_orders &gt;= 2.</t>
+  </si>
+  <si>
+    <t>Repeat customer flag.</t>
+  </si>
+  <si>
+    <t>ever_subscribed</t>
+  </si>
+  <si>
+    <t>is_subscription (derived)</t>
+  </si>
+  <si>
+    <t>ANY(is_subscription) GROUP BY customer_id.</t>
+  </si>
+  <si>
+    <t>Ever had a Shopify subscription order.</t>
+  </si>
+  <si>
+    <t>first_channel</t>
+  </si>
+  <si>
+    <t>channel (derived)</t>
+  </si>
+  <si>
+    <t>FIRST channel by order_date per customer.</t>
+  </si>
+  <si>
+    <t>Acquisition channel for LTV-by-channel analysis.</t>
+  </si>
+  <si>
+    <t>cohort_month</t>
+  </si>
+  <si>
+    <t>PERIOD</t>
+  </si>
+  <si>
+    <t>first_order_date (derived)</t>
+  </si>
+  <si>
+    <t>period</t>
+  </si>
+  <si>
+    <t>first_order_date.to_period(M).</t>
+  </si>
+  <si>
+    <t>Monthly acquisition cohort key.</t>
   </si>
 </sst>
 </file>
@@ -184,8 +649,6 @@
   </cellStyleXfs>
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -195,6 +658,8 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -532,449 +997,929 @@
   <dimension ref="A1:H40"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="5" max="5" width="30" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="50" customWidth="1"/>
-    <col min="8" max="8" width="60" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="41.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="65.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="89.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
     </row>
     <row r="2" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
+      <c r="A6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>31</v>
+      </c>
+      <c r="H6" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="4"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="A7" t="s">
+        <v>33</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G7" t="s">
+        <v>36</v>
+      </c>
+      <c r="H7" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="4"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4"/>
-      <c r="H8" s="4"/>
+      <c r="A8" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" t="s">
+        <v>40</v>
+      </c>
+      <c r="H8" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="4"/>
+      <c r="A9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" t="s">
+        <v>46</v>
+      </c>
+      <c r="H9" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="4"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
+        <v>43</v>
+      </c>
+      <c r="D10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G10" t="s">
+        <v>50</v>
+      </c>
+      <c r="H10" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="4"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4"/>
-      <c r="H11" s="4"/>
+      <c r="A11" t="s">
+        <v>52</v>
+      </c>
+      <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" t="s">
+        <v>45</v>
+      </c>
+      <c r="G11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4"/>
-      <c r="H12" s="4"/>
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
+      <c r="A13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" t="s">
+        <v>61</v>
+      </c>
+      <c r="H13" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
+      <c r="A14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G14" t="s">
+        <v>66</v>
+      </c>
+      <c r="H14" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
+      <c r="A15" t="s">
+        <v>68</v>
+      </c>
+      <c r="B15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
+      <c r="A16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G16" t="s">
+        <v>74</v>
+      </c>
+      <c r="H16" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="4"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
+      <c r="A17" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" t="s">
+        <v>20</v>
+      </c>
+      <c r="G17" t="s">
+        <v>74</v>
+      </c>
+      <c r="H17" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
+      <c r="A18" t="s">
+        <v>79</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G18" t="s">
+        <v>74</v>
+      </c>
+      <c r="H18" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="4"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
+      <c r="A19" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" t="s">
+        <v>83</v>
+      </c>
+      <c r="F19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" t="s">
+        <v>74</v>
+      </c>
+      <c r="H19" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="4"/>
-      <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="4"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
+      <c r="A20" t="s">
+        <v>85</v>
+      </c>
+      <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D20" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" t="s">
+        <v>86</v>
+      </c>
+      <c r="F20" t="s">
+        <v>87</v>
+      </c>
+      <c r="G20" t="s">
+        <v>88</v>
+      </c>
+      <c r="H20" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="4"/>
-      <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="4"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
+      <c r="A21" t="s">
+        <v>90</v>
+      </c>
+      <c r="B21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" t="s">
+        <v>91</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" t="s">
+        <v>92</v>
+      </c>
+      <c r="H21" t="s">
+        <v>93</v>
+      </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="4"/>
-      <c r="D22" s="4"/>
-      <c r="E22" s="4"/>
-      <c r="F22" s="4"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
+      <c r="A22" t="s">
+        <v>94</v>
+      </c>
+      <c r="B22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" t="s">
+        <v>95</v>
+      </c>
+      <c r="F22" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" t="s">
+        <v>96</v>
+      </c>
+      <c r="H22" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
+      <c r="A23" t="s">
+        <v>98</v>
+      </c>
+      <c r="B23" t="s">
+        <v>99</v>
+      </c>
+      <c r="D23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" t="s">
+        <v>100</v>
+      </c>
+      <c r="F23" t="s">
+        <v>101</v>
+      </c>
+      <c r="G23" t="s">
+        <v>102</v>
+      </c>
+      <c r="H23" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A24" s="4"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
+      <c r="A24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" t="s">
+        <v>105</v>
+      </c>
+      <c r="F24" t="s">
+        <v>101</v>
+      </c>
+      <c r="G24" t="s">
+        <v>106</v>
+      </c>
+      <c r="H24" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="4"/>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4"/>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
+      <c r="A25" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" t="s">
+        <v>99</v>
+      </c>
+      <c r="D25" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" t="s">
+        <v>105</v>
+      </c>
+      <c r="F25" t="s">
+        <v>101</v>
+      </c>
+      <c r="G25" t="s">
+        <v>109</v>
+      </c>
+      <c r="H25" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="4"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
+      <c r="A26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" t="s">
+        <v>112</v>
+      </c>
+      <c r="D26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" t="s">
+        <v>113</v>
+      </c>
+      <c r="F26" t="s">
+        <v>114</v>
+      </c>
+      <c r="G26" t="s">
+        <v>115</v>
+      </c>
+      <c r="H26" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="4"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="4"/>
+      <c r="A27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" t="s">
+        <v>18</v>
+      </c>
+      <c r="C27" t="s">
+        <v>118</v>
+      </c>
+      <c r="D27" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" t="s">
+        <v>119</v>
+      </c>
+      <c r="F27" t="s">
+        <v>120</v>
+      </c>
+      <c r="G27" t="s">
+        <v>121</v>
+      </c>
+      <c r="H27" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A28" s="4"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="4"/>
+      <c r="A28" t="s">
+        <v>123</v>
+      </c>
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28" t="s">
+        <v>118</v>
+      </c>
+      <c r="D28" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" t="s">
+        <v>124</v>
+      </c>
+      <c r="F28" t="s">
+        <v>20</v>
+      </c>
+      <c r="G28" t="s">
+        <v>125</v>
+      </c>
+      <c r="H28" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="4"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="4"/>
+      <c r="A29" t="s">
+        <v>127</v>
+      </c>
+      <c r="B29" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" t="s">
+        <v>128</v>
+      </c>
+      <c r="F29" t="s">
+        <v>20</v>
+      </c>
+      <c r="G29" t="s">
+        <v>121</v>
+      </c>
+      <c r="H29" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="4"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="4"/>
+      <c r="A30" t="s">
+        <v>130</v>
+      </c>
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="D30" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" t="s">
+        <v>131</v>
+      </c>
+      <c r="F30" t="s">
+        <v>20</v>
+      </c>
+      <c r="G30" t="s">
+        <v>121</v>
+      </c>
+      <c r="H30" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="4"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
+      <c r="A31" t="s">
+        <v>133</v>
+      </c>
+      <c r="B31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D31" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" t="s">
+        <v>135</v>
+      </c>
+      <c r="F31" t="s">
+        <v>136</v>
+      </c>
+      <c r="G31" t="s">
+        <v>137</v>
+      </c>
+      <c r="H31" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="4"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
+      <c r="A32" t="s">
+        <v>139</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" t="s">
+        <v>140</v>
+      </c>
+      <c r="F32" t="s">
+        <v>45</v>
+      </c>
+      <c r="G32" t="s">
+        <v>141</v>
+      </c>
+      <c r="H32" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="4"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
+      <c r="A33" t="s">
+        <v>143</v>
+      </c>
+      <c r="B33" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" t="s">
+        <v>144</v>
+      </c>
+      <c r="F33" t="s">
+        <v>45</v>
+      </c>
+      <c r="G33" t="s">
+        <v>50</v>
+      </c>
+      <c r="H33" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="4"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
+      <c r="A34" t="s">
+        <v>146</v>
+      </c>
+      <c r="B34" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" t="s">
+        <v>147</v>
+      </c>
+      <c r="F34" t="s">
+        <v>45</v>
+      </c>
+      <c r="G34" t="s">
+        <v>141</v>
+      </c>
+      <c r="H34" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="4"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
+      <c r="A35" t="s">
+        <v>149</v>
+      </c>
+      <c r="B35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" t="s">
+        <v>150</v>
+      </c>
+      <c r="E35" t="s">
+        <v>44</v>
+      </c>
+      <c r="F35" t="s">
+        <v>45</v>
+      </c>
+      <c r="G35" t="s">
+        <v>151</v>
+      </c>
+      <c r="H35" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="4"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
+      <c r="A36" t="s">
+        <v>153</v>
+      </c>
+      <c r="B36" t="s">
+        <v>99</v>
+      </c>
+      <c r="D36" t="s">
+        <v>154</v>
+      </c>
+      <c r="E36" t="s">
+        <v>155</v>
+      </c>
+      <c r="F36" t="s">
+        <v>101</v>
+      </c>
+      <c r="G36" t="s">
+        <v>156</v>
+      </c>
+      <c r="H36" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="4"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
+      <c r="A37" t="s">
+        <v>158</v>
+      </c>
+      <c r="B37" t="s">
+        <v>99</v>
+      </c>
+      <c r="D37" t="s">
+        <v>154</v>
+      </c>
+      <c r="E37" t="s">
+        <v>159</v>
+      </c>
+      <c r="F37" t="s">
+        <v>101</v>
+      </c>
+      <c r="G37" t="s">
+        <v>160</v>
+      </c>
+      <c r="H37" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="4"/>
-      <c r="B38" s="4"/>
-      <c r="C38" s="4"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
-      <c r="G38" s="4"/>
-      <c r="H38" s="4"/>
+      <c r="A38" t="s">
+        <v>162</v>
+      </c>
+      <c r="B38" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" t="s">
+        <v>154</v>
+      </c>
+      <c r="E38" t="s">
+        <v>163</v>
+      </c>
+      <c r="F38" t="s">
+        <v>20</v>
+      </c>
+      <c r="G38" t="s">
+        <v>164</v>
+      </c>
+      <c r="H38" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="4"/>
-      <c r="B39" s="4"/>
-      <c r="C39" s="4"/>
-      <c r="D39" s="4"/>
-      <c r="E39" s="4"/>
-      <c r="F39" s="4"/>
-      <c r="G39" s="4"/>
-      <c r="H39" s="4"/>
+      <c r="A39" t="s">
+        <v>166</v>
+      </c>
+      <c r="B39" t="s">
+        <v>167</v>
+      </c>
+      <c r="D39" t="s">
+        <v>154</v>
+      </c>
+      <c r="E39" t="s">
+        <v>168</v>
+      </c>
+      <c r="F39" t="s">
+        <v>169</v>
+      </c>
+      <c r="G39" t="s">
+        <v>170</v>
+      </c>
+      <c r="H39" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
-      <c r="D40" s="4"/>
-      <c r="E40" s="4"/>
-      <c r="F40" s="4"/>
-      <c r="G40" s="4"/>
-      <c r="H40" s="4"/>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
